--- a/slide_classification/TCGA_Results/PRISM/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/PRISM/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -9209,7 +9209,7 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>0.18571</v>
+        <v>0.333333</v>
       </c>
       <c r="J204" t="n">
         <v>1</v>
@@ -9295,7 +9295,7 @@
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>0.161058</v>
+        <v>0</v>
       </c>
       <c r="J206" t="n">
         <v>1</v>
@@ -9338,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="I207" t="n">
-        <v>0.197436</v>
+        <v>0.333333</v>
       </c>
       <c r="J207" t="n">
         <v>1</v>
@@ -9381,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>0.187239</v>
+        <v>0</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -9467,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>0.417107</v>
+        <v>0.333333</v>
       </c>
       <c r="J210" t="n">
         <v>1</v>
@@ -9811,7 +9811,7 @@
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>0.232557</v>
+        <v>0.333333</v>
       </c>
       <c r="J218" t="n">
         <v>1</v>
@@ -9980,10 +9980,10 @@
         <v>0.864042</v>
       </c>
       <c r="H222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I222" t="n">
-        <v>0.440246</v>
+        <v>0.666667</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -10069,7 +10069,7 @@
         <v>0</v>
       </c>
       <c r="I224" t="n">
-        <v>0.450205</v>
+        <v>0.333333</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -10112,7 +10112,7 @@
         <v>0</v>
       </c>
       <c r="I225" t="n">
-        <v>0.173956</v>
+        <v>0</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -10886,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="I243" t="n">
-        <v>0.219299</v>
+        <v>0.333333</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -10972,7 +10972,7 @@
         <v>0</v>
       </c>
       <c r="I245" t="n">
-        <v>0.202209</v>
+        <v>0.333333</v>
       </c>
       <c r="J245" t="n">
         <v>1</v>
@@ -11015,7 +11015,7 @@
         <v>0</v>
       </c>
       <c r="I246" t="n">
-        <v>0.183547</v>
+        <v>0</v>
       </c>
       <c r="J246" t="n">
         <v>1</v>
@@ -11101,7 +11101,7 @@
         <v>0</v>
       </c>
       <c r="I248" t="n">
-        <v>0.192266</v>
+        <v>0.333333</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
         <v>0</v>
       </c>
       <c r="I251" t="n">
-        <v>0.146652</v>
+        <v>0</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>0.194242</v>
+        <v>0</v>
       </c>
       <c r="J252" t="n">
         <v>1</v>
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="I254" t="n">
-        <v>0.214076</v>
+        <v>0.333333</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -11402,7 +11402,7 @@
         <v>0</v>
       </c>
       <c r="I255" t="n">
-        <v>0.186199</v>
+        <v>0</v>
       </c>
       <c r="J255" t="n">
         <v>1</v>
@@ -11445,7 +11445,7 @@
         <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>0.169666</v>
+        <v>0</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -11488,7 +11488,7 @@
         <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>0.256442</v>
+        <v>0.333333</v>
       </c>
       <c r="J257" t="n">
         <v>1</v>
@@ -11531,7 +11531,7 @@
         <v>1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.807609</v>
+        <v>0.666667</v>
       </c>
       <c r="J258" t="n">
         <v>1</v>
@@ -11703,7 +11703,7 @@
         <v>0</v>
       </c>
       <c r="I262" t="n">
-        <v>0.202924</v>
+        <v>0.333333</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -11789,7 +11789,7 @@
         <v>0</v>
       </c>
       <c r="I264" t="n">
-        <v>0.398683</v>
+        <v>0.333333</v>
       </c>
       <c r="J264" t="n">
         <v>1</v>
@@ -11918,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>0.226485</v>
+        <v>0.333333</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -11961,7 +11961,7 @@
         <v>0</v>
       </c>
       <c r="I268" t="n">
-        <v>0.148718</v>
+        <v>0</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -12133,7 +12133,7 @@
         <v>0</v>
       </c>
       <c r="I272" t="n">
-        <v>0.190229</v>
+        <v>0</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -12219,7 +12219,7 @@
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>0.194559</v>
+        <v>0</v>
       </c>
       <c r="J274" t="n">
         <v>1</v>
@@ -12262,7 +12262,7 @@
         <v>0</v>
       </c>
       <c r="I275" t="n">
-        <v>0.185799</v>
+        <v>0</v>
       </c>
       <c r="J275" t="n">
         <v>1</v>
@@ -12305,7 +12305,7 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>0.182816</v>
+        <v>0</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>0.192059</v>
+        <v>0.333333</v>
       </c>
       <c r="J281" t="n">
         <v>1</v>
@@ -12606,7 +12606,7 @@
         <v>0</v>
       </c>
       <c r="I283" t="n">
-        <v>0.214491</v>
+        <v>0.333333</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -12735,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="I286" t="n">
-        <v>0.182182</v>
+        <v>0</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -12907,7 +12907,7 @@
         <v>0</v>
       </c>
       <c r="I290" t="n">
-        <v>0.176846</v>
+        <v>0</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -12993,7 +12993,7 @@
         <v>0</v>
       </c>
       <c r="I292" t="n">
-        <v>0.191289</v>
+        <v>0</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -13036,7 +13036,7 @@
         <v>0</v>
       </c>
       <c r="I293" t="n">
-        <v>0.217323</v>
+        <v>0.333333</v>
       </c>
       <c r="J293" t="n">
         <v>1</v>
@@ -13165,7 +13165,7 @@
         <v>1</v>
       </c>
       <c r="I296" t="n">
-        <v>0.611483</v>
+        <v>0.666667</v>
       </c>
       <c r="J296" t="n">
         <v>1</v>
@@ -13291,10 +13291,10 @@
         <v>0.40978</v>
       </c>
       <c r="H299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I299" t="n">
-        <v>0.385621</v>
+        <v>0.666667</v>
       </c>
       <c r="J299" t="n">
         <v>1</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="I300" t="n">
-        <v>0.278598</v>
+        <v>0.333333</v>
       </c>
       <c r="J300" t="n">
         <v>1</v>
@@ -13423,7 +13423,7 @@
         <v>0</v>
       </c>
       <c r="I302" t="n">
-        <v>0.390997</v>
+        <v>0.333333</v>
       </c>
       <c r="J302" t="n">
         <v>1</v>
@@ -13466,7 +13466,7 @@
         <v>0</v>
       </c>
       <c r="I303" t="n">
-        <v>0.370539</v>
+        <v>0.333333</v>
       </c>
       <c r="J303" t="n">
         <v>0</v>
@@ -13509,7 +13509,7 @@
         <v>0</v>
       </c>
       <c r="I304" t="n">
-        <v>0.147628</v>
+        <v>0</v>
       </c>
       <c r="J304" t="n">
         <v>0</v>
@@ -13595,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="I306" t="n">
-        <v>0.188431</v>
+        <v>0</v>
       </c>
       <c r="J306" t="n">
         <v>0</v>
@@ -13681,7 +13681,7 @@
         <v>0</v>
       </c>
       <c r="I308" t="n">
-        <v>0.387808</v>
+        <v>0.333333</v>
       </c>
       <c r="J308" t="n">
         <v>0</v>
@@ -13724,7 +13724,7 @@
         <v>0</v>
       </c>
       <c r="I309" t="n">
-        <v>0.225613</v>
+        <v>0.333333</v>
       </c>
       <c r="J309" t="n">
         <v>0</v>
@@ -13810,7 +13810,7 @@
         <v>0</v>
       </c>
       <c r="I311" t="n">
-        <v>0.215669</v>
+        <v>0.333333</v>
       </c>
       <c r="J311" t="n">
         <v>0</v>
@@ -17978,10 +17978,10 @@
         <v>0.954739</v>
       </c>
       <c r="H408" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I408" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J408" t="n">
         <v>0</v>

--- a/slide_classification/TCGA_Results/PRISM/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/PRISM/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.231841</v>
+        <v>0.318866</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.848881</v>
+        <v>0.961336</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.10988</v>
+        <v>0.126625</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -643,10 +643,10 @@
         <v>0.001782</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.313978</v>
+        <v>0.694717</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.43952</v>
+        <v>0.443701</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.677364</v>
+        <v>0.844678</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.152908</v>
+        <v>0.130603</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.268331</v>
+        <v>0.14597</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.525813</v>
+        <v>0.664224</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.141522</v>
+        <v>0.137748</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.98678</v>
+        <v>0.986554</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -987,10 +987,10 @@
         <v>0.001274</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.547794</v>
+        <v>0.260833</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.230393</v>
+        <v>0.170709</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.193434</v>
+        <v>0.208531</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.526779</v>
+        <v>0.531949</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.167431</v>
+        <v>0.165915</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.279264</v>
+        <v>0.320159</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.167852</v>
+        <v>0.179193</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.148508</v>
+        <v>0.138387</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.370988</v>
+        <v>0.442963</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6857569999999999</v>
+        <v>0.871545</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2219</v>
+        <v>0.261366</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.337599</v>
+        <v>0.23847</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
         <v>0.001006</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.589385</v>
+        <v>0.337394</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.142574</v>
+        <v>0.153686</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.185958</v>
+        <v>0.234822</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.331964</v>
+        <v>0.369857</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.231159</v>
+        <v>0.338081</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9174020000000001</v>
+        <v>0.98409</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.201494</v>
+        <v>0.169983</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.257818</v>
+        <v>0.280689</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.440898</v>
+        <v>0.464627</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.312775</v>
+        <v>0.329965</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.271228</v>
+        <v>0.394493</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.245847</v>
+        <v>0.264827</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.267552</v>
+        <v>0.263018</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.200208</v>
+        <v>0.250247</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1029</v>
+        <v>0.077074</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.217426</v>
+        <v>0.431681</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.215777</v>
+        <v>0.260099</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.175726</v>
+        <v>0.12222</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.159684</v>
+        <v>0.254601</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.319608</v>
+        <v>0.345403</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.286978</v>
+        <v>0.265258</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.289316</v>
+        <v>0.455418</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.234117</v>
+        <v>0.259316</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.702435</v>
+        <v>0.666981</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.29958</v>
+        <v>0.22804</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.311122</v>
+        <v>0.325851</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.41782</v>
+        <v>0.486134</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.90808</v>
+        <v>0.962583</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.188445</v>
+        <v>0.177973</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.254266</v>
+        <v>0.228236</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0.732183</v>
+        <v>0.676877</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.109119</v>
+        <v>0.139971</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7944329999999999</v>
+        <v>0.803081</v>
       </c>
       <c r="H57" t="n">
         <v>1</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.184855</v>
+        <v>0.209957</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.492767</v>
+        <v>0.395573</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3008,10 +3008,10 @@
         <v>0.000186</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.295846</v>
+        <v>0.61528</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.999861</v>
+        <v>0.999906</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.223035</v>
+        <v>0.363814</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.996835</v>
+        <v>0.997841</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3180,10 +3180,10 @@
         <v>0.151587</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.456344</v>
+        <v>0.533048</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0.540872</v>
+        <v>0.576308</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.234304</v>
+        <v>0.285901</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.197733</v>
+        <v>0.198564</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.413065</v>
+        <v>0.401609</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.283043</v>
+        <v>0.299597</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.270275</v>
+        <v>0.309325</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3481,10 +3481,10 @@
         <v>0.59561</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.329986</v>
+        <v>0.507103</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.215217</v>
+        <v>0.175934</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.242134</v>
+        <v>0.199482</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.887145</v>
+        <v>0.91881</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.243977</v>
+        <v>0.29333</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.174024</v>
+        <v>0.240608</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.774446</v>
+        <v>0.917571</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3782,10 +3782,10 @@
         <v>0.975711</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.495487</v>
+        <v>0.550909</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.294803</v>
+        <v>0.462709</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.200381</v>
+        <v>0.330597</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.291273</v>
+        <v>0.359304</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.53791</v>
+        <v>0.573877</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.225534</v>
+        <v>0.471004</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.229804</v>
+        <v>0.341425</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.190463</v>
+        <v>0.273988</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0.95919</v>
+        <v>0.997557</v>
       </c>
       <c r="H86" t="n">
         <v>1</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.205303</v>
+        <v>0.120784</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.111443</v>
+        <v>0.136212</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.9974730000000001</v>
+        <v>0.999925</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.118486</v>
+        <v>0.143218</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.170962</v>
+        <v>0.21818</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.34728</v>
+        <v>0.402617</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.210895</v>
+        <v>0.21994</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.205653</v>
+        <v>0.199382</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0.543508</v>
+        <v>0.62869</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.268521</v>
+        <v>0.302019</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.181831</v>
+        <v>0.182473</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0.352269</v>
+        <v>0.372344</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.915903</v>
+        <v>0.947294</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.243434</v>
+        <v>0.283544</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.837506</v>
+        <v>0.841693</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.910725</v>
+        <v>0.93505</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.243569</v>
+        <v>0.27949</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.222794</v>
+        <v>0.217524</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.177672</v>
+        <v>0.164978</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.238725</v>
+        <v>0.204223</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.396801</v>
+        <v>0.356902</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.641333</v>
+        <v>0.649295</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.300903</v>
+        <v>0.207748</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.746759</v>
+        <v>0.813802</v>
       </c>
       <c r="H110" t="n">
         <v>1</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.209363</v>
+        <v>0.142202</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.191024</v>
+        <v>0.115491</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.26536</v>
+        <v>0.267743</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.222101</v>
+        <v>0.189698</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.157048</v>
+        <v>0.127674</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.170466</v>
+        <v>0.159426</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.268809</v>
+        <v>0.196385</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.182499</v>
+        <v>0.195227</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.9096610000000001</v>
+        <v>0.8572920000000001</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.215544</v>
+        <v>0.213133</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5631,10 +5631,10 @@
         <v>0.039651</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.70046</v>
+        <v>0.492603</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.838275</v>
+        <v>0.836885</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.720962</v>
+        <v>0.539921</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.283628</v>
+        <v>0.111863</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.237076</v>
+        <v>0.254745</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.195213</v>
+        <v>0.187851</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.163228</v>
+        <v>0.150659</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.128656</v>
+        <v>0.16729</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.575204</v>
+        <v>0.626857</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.293349</v>
+        <v>0.341708</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.285644</v>
+        <v>0.219299</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.236057</v>
+        <v>0.242242</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.216718</v>
+        <v>0.171127</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.290946</v>
+        <v>0.152405</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.313827</v>
+        <v>0.347496</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.200932</v>
+        <v>0.204402</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.269978</v>
+        <v>0.250441</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.15514</v>
+        <v>0.108433</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0.8750019999999999</v>
+        <v>0.84674</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.233071</v>
+        <v>0.14541</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.161544</v>
+        <v>0.154075</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.155277</v>
+        <v>0.070548</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.28853</v>
+        <v>0.343137</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.27576</v>
+        <v>0.161479</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.275628</v>
+        <v>0.086896</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.251813</v>
+        <v>0.364782</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.216774</v>
+        <v>0.155615</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.252429</v>
+        <v>0.198997</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0.554968</v>
+        <v>0.60295</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.247994</v>
+        <v>0.230029</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.293001</v>
+        <v>0.230029</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.9996080000000001</v>
+        <v>0.999895</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.226056</v>
+        <v>0.244361</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.157931</v>
+        <v>0.096845</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.2685</v>
+        <v>0.124508</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.21496</v>
+        <v>0.196558</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.278512</v>
+        <v>0.192518</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.204579</v>
+        <v>0.115619</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.264088</v>
+        <v>0.166331</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.293506</v>
+        <v>0.28757</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.19652</v>
+        <v>0.133385</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.213942</v>
+        <v>0.190468</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.207523</v>
+        <v>0.18042</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0.979921</v>
+        <v>0.999768</v>
       </c>
       <c r="H164" t="n">
         <v>1</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.153063</v>
+        <v>0.157412</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.378178</v>
+        <v>0.405656</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.179344</v>
+        <v>0.122938</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.96546</v>
+        <v>0.99486</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.282808</v>
+        <v>0.29902</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.14913</v>
+        <v>0.081342</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.303135</v>
+        <v>0.257193</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.155593</v>
+        <v>0.172382</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.256055</v>
+        <v>0.2458</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.162794</v>
+        <v>0.145867</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.212035</v>
+        <v>0.159722</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.215778</v>
+        <v>0.197947</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.26465</v>
+        <v>0.126169</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.164999</v>
+        <v>0.118353</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.278482</v>
+        <v>0.130596</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.190944</v>
+        <v>0.218961</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.350709</v>
+        <v>0.227347</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0.600957</v>
+        <v>0.869518</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.230802</v>
+        <v>0.207213</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.287257</v>
+        <v>0.311937</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.307611</v>
+        <v>0.18908</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.220058</v>
+        <v>0.218583</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8469,10 +8469,10 @@
         <v>0.036962</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0.344652</v>
+        <v>0.564564</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.255483</v>
+        <v>0.221482</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.134013</v>
+        <v>0.062805</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.97098</v>
+        <v>0.99139</v>
       </c>
       <c r="H190" t="n">
         <v>1</v>
@@ -8644,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.438104</v>
+        <v>0.363178</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.281887</v>
+        <v>0.192769</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0.215586</v>
+        <v>0.054495</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.123299</v>
+        <v>0.116548</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.122037</v>
+        <v>0.122036</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.322783</v>
+        <v>0.264382</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.847653</v>
+        <v>0.933596</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>0.353314</v>
+        <v>0.369398</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.7573260000000001</v>
+        <v>0.739453</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.351328</v>
+        <v>0.353007</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.258831</v>
+        <v>0.210967</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.169903</v>
+        <v>0.192221</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.358725</v>
+        <v>0.220429</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.355669</v>
+        <v>0.328939</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.253717</v>
+        <v>0.18621</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14105,7 +14105,7 @@
         <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>0.260481</v>
+        <v>0.29096</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.323817</v>
+        <v>0.466163</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14188,10 +14188,10 @@
         <v>0.994046</v>
       </c>
       <c r="F320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G320" t="n">
-        <v>0.6795679999999999</v>
+        <v>0.403095</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.257598</v>
+        <v>0.211094</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.28487</v>
+        <v>0.188272</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.147335</v>
+        <v>0.06561400000000001</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>0.750348</v>
+        <v>0.70231</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.22468</v>
+        <v>0.207111</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.268016</v>
+        <v>0.272764</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.174256</v>
+        <v>0.109556</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.983836</v>
+        <v>0.965821</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.461066</v>
+        <v>0.427954</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.32367</v>
+        <v>0.199608</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.99999</v>
+        <v>0.999982</v>
       </c>
       <c r="H331" t="n">
         <v>1</v>
@@ -14704,10 +14704,10 @@
         <v>0.543588</v>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.523323</v>
+        <v>0.35743</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.992471</v>
+        <v>0.999869</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14790,10 +14790,10 @@
         <v>0.002874</v>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.53569</v>
+        <v>0.435767</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.30508</v>
+        <v>0.284618</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.311452</v>
+        <v>0.19723</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.194148</v>
+        <v>0.150182</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.207762</v>
+        <v>0.104819</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.355911</v>
+        <v>0.226253</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15048,10 +15048,10 @@
         <v>0.66083</v>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.565921</v>
+        <v>0.425879</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.177407</v>
+        <v>0.143392</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.204605</v>
+        <v>0.169842</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.321171</v>
+        <v>0.461036</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.317664</v>
+        <v>0.437629</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0.841593</v>
+        <v>0.823465</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.196766</v>
+        <v>0.072209</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.47139</v>
+        <v>0.219702</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0.797392</v>
+        <v>0.830091</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0.986474</v>
+        <v>0.994625</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.5806750000000001</v>
+        <v>0.585236</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.441277</v>
+        <v>0.385686</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.203419</v>
+        <v>0.082705</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.206771</v>
+        <v>0.108328</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.202015</v>
+        <v>0.118382</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.171659</v>
+        <v>0.116843</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.207479</v>
+        <v>0.104708</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.180985</v>
+        <v>0.11812</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>0.988823</v>
+        <v>0.999532</v>
       </c>
       <c r="H358" t="n">
         <v>1</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.179478</v>
+        <v>0.102175</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>0.212202</v>
+        <v>0.125468</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0.273169</v>
+        <v>0.214326</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15994,10 +15994,10 @@
         <v>0.007454</v>
       </c>
       <c r="F362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G362" t="n">
-        <v>0.533481</v>
+        <v>0.401793</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.200941</v>
+        <v>0.168</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.983368</v>
+        <v>0.94087</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.203541</v>
+        <v>0.139258</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.239159</v>
+        <v>0.192507</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.294702</v>
+        <v>0.219751</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.255969</v>
+        <v>0.144442</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.350177</v>
+        <v>0.292137</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.227342</v>
+        <v>0.247833</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0.612853</v>
+        <v>0.565289</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.28607</v>
+        <v>0.200022</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.260548</v>
+        <v>0.203559</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.379848</v>
+        <v>0.137307</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.1998</v>
+        <v>0.118813</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.341975</v>
+        <v>0.354962</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.205337</v>
+        <v>0.194397</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.399997</v>
+        <v>0.224077</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.230907</v>
+        <v>0.163123</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0.655603</v>
+        <v>0.512733</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.463566</v>
+        <v>0.350589</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>0.290924</v>
+        <v>0.470581</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.227182</v>
+        <v>0.197059</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.197203</v>
+        <v>0.142798</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.201778</v>
+        <v>0.13425</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.182778</v>
+        <v>0.159704</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.272661</v>
+        <v>0.173358</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.253317</v>
+        <v>0.147739</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.145766</v>
+        <v>0.163189</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.352704</v>
+        <v>0.280649</v>
       </c>
       <c r="H390" t="n">
         <v>1</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.227504</v>
+        <v>0.211376</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="G392" t="n">
-        <v>0.114181</v>
+        <v>0.092529</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.778953</v>
+        <v>0.951423</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.219431</v>
+        <v>0.07395699999999999</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.8675929999999999</v>
+        <v>0.718013</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.235932</v>
+        <v>0.158989</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0.904887</v>
+        <v>0.971038</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.318648</v>
+        <v>0.235804</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17585,10 +17585,10 @@
         <v>0.225422</v>
       </c>
       <c r="F399" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.512761</v>
+        <v>0.441174</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.416288</v>
+        <v>0.255553</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.314768</v>
+        <v>0.26369</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.210206</v>
+        <v>0.128159</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.526635</v>
+        <v>0.57931</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.230938</v>
+        <v>0.158781</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.247604</v>
+        <v>0.156254</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.227416</v>
+        <v>0.123</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0.985464</v>
+        <v>0.969714</v>
       </c>
       <c r="H407" t="n">
         <v>1</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.954739</v>
+        <v>0.92406</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.483226</v>
+        <v>0.458415</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.162774</v>
+        <v>0.07154099999999999</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>0.444731</v>
+        <v>0.331174</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18144,10 +18144,10 @@
         <v>0.077136</v>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G412" t="n">
-        <v>0.5819029999999999</v>
+        <v>0.45569</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.327214</v>
+        <v>0.238624</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.997262</v>
+        <v>0.975159</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
